--- a/Функция_Режим.xlsx
+++ b/Функция_Режим.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="SGF_Parameters" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Settings" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="Inputs" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="Outputs" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="SGF_Parameters" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Settings" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Inputs" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Outputs" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -435,7 +435,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AX2"/>
+  <dimension ref="A1:AU2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -485,140 +485,137 @@
     <col width="20" customWidth="1" min="45" max="45"/>
     <col width="20" customWidth="1" min="46" max="46"/>
     <col width="20" customWidth="1" min="47" max="47"/>
-    <col width="20" customWidth="1" min="48" max="48"/>
-    <col width="20" customWidth="1" min="49" max="49"/>
-    <col width="20" customWidth="1" min="50" max="50"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>SGF1_lvttoc(Сборка_ток_цепей)</t>
+          <t>SGF1_lvttoc</t>
         </is>
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>SGF1_ptoc1</t>
+          <t>SGF1_ptoc1_lvttoc</t>
         </is>
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>SGF2_ptoc1</t>
+          <t>SGF2_ptoc1_lvttoc</t>
         </is>
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>SGF3_ptoc1</t>
+          <t>SGF3_ptoc1_lvttoc</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>SGF4_ptoc1</t>
+          <t>SGF4_ptoc1_lvttoc</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>SGF5_ptoc1</t>
+          <t>SGF5_ptoc1_lvttoc</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
-          <t>SGF6_ptoc1</t>
+          <t>SGF6_ptoc1_lvttoc</t>
         </is>
       </c>
       <c r="H1" s="1" t="inlineStr">
         <is>
-          <t>SGF7_ptoc1</t>
+          <t>SGF7_ptoc1_lvttoc</t>
         </is>
       </c>
       <c r="I1" s="1" t="inlineStr">
         <is>
-          <t>SGF1_ptoc2</t>
+          <t>SGF1_ptoc2_lvttoc</t>
         </is>
       </c>
       <c r="J1" s="1" t="inlineStr">
         <is>
-          <t>SGF2_ptoc2</t>
+          <t>SGF2_ptoc2_lvttoc</t>
         </is>
       </c>
       <c r="K1" s="1" t="inlineStr">
         <is>
-          <t>SGF3_ptoc2</t>
+          <t>SGF3_ptoc2_lvttoc</t>
         </is>
       </c>
       <c r="L1" s="1" t="inlineStr">
         <is>
-          <t>SGF4_ptoc2</t>
+          <t>SGF4_ptoc2_lvttoc</t>
         </is>
       </c>
       <c r="M1" s="1" t="inlineStr">
         <is>
-          <t>SGF5_ptoc2</t>
+          <t>SGF5_ptoc2_lvttoc</t>
         </is>
       </c>
       <c r="N1" s="1" t="inlineStr">
         <is>
-          <t>SGF6_ptoc2</t>
+          <t>SGF6_ptoc2_lvttoc</t>
         </is>
       </c>
       <c r="O1" s="1" t="inlineStr">
         <is>
-          <t>SGF7_ptoc2</t>
+          <t>SGF7_ptoc2_lvttoc</t>
         </is>
       </c>
       <c r="P1" s="1" t="inlineStr">
         <is>
-          <t>SGF1_ptoc3</t>
+          <t>SGF1_ptoc3_lvttoc</t>
         </is>
       </c>
       <c r="Q1" s="1" t="inlineStr">
         <is>
-          <t>SGF2_ptoc3</t>
+          <t>SGF2_ptoc3_lvttoc</t>
         </is>
       </c>
       <c r="R1" s="1" t="inlineStr">
         <is>
-          <t>SGF3_ptoc3</t>
+          <t>SGF3_ptoc3_lvttoc</t>
         </is>
       </c>
       <c r="S1" s="1" t="inlineStr">
         <is>
-          <t>SGF4_ptoc3</t>
+          <t>SGF4_ptoc3_lvttoc</t>
         </is>
       </c>
       <c r="T1" s="1" t="inlineStr">
         <is>
-          <t>SGF5_ptoc3</t>
+          <t>SGF5_ptoc3_lvttoc</t>
         </is>
       </c>
       <c r="U1" s="1" t="inlineStr">
         <is>
-          <t>SGF6_ptoc3</t>
+          <t>SGF6_ptoc3_lvttoc</t>
         </is>
       </c>
       <c r="V1" s="1" t="inlineStr">
         <is>
-          <t>SGF7_ptoc3</t>
+          <t>SGF7_ptoc3_lvttoc</t>
         </is>
       </c>
       <c r="W1" s="1" t="inlineStr">
         <is>
-          <t>SGF1_ptuv1</t>
+          <t>SGF1_ptuv1_lvttoc</t>
         </is>
       </c>
       <c r="X1" s="1" t="inlineStr">
         <is>
-          <t>SGF1_ptuv2</t>
+          <t>SGF1_ptuv2_lvttoc</t>
         </is>
       </c>
       <c r="Y1" s="1" t="inlineStr">
         <is>
-          <t>SGF1_phar1</t>
+          <t>SGF1_phar1_lvttoc</t>
         </is>
       </c>
       <c r="Z1" s="1" t="inlineStr">
         <is>
-          <t>SGF1_rblc1</t>
+          <t>SGF1_rblc1_lvttoc</t>
         </is>
       </c>
       <c r="AA1" s="1" t="inlineStr">
@@ -724,21 +721,6 @@
       <c r="AU1" s="1" t="inlineStr">
         <is>
           <t>SGF10_lvalv</t>
-        </is>
-      </c>
-      <c r="AV1" s="1" t="inlineStr">
-        <is>
-          <t>SGF11_lvalv</t>
-        </is>
-      </c>
-      <c r="AW1" s="1" t="inlineStr">
-        <is>
-          <t>SGF12_lvalv</t>
-        </is>
-      </c>
-      <c r="AX1" s="1" t="inlineStr">
-        <is>
-          <t>SGF13_lvalv</t>
         </is>
       </c>
     </row>
@@ -882,15 +864,6 @@
         <v>0</v>
       </c>
       <c r="AU2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX2" t="n">
         <v>0</v>
       </c>
     </row>
@@ -934,77 +907,77 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>T1_ptoc1</t>
+          <t>T1_ptoc1_lvttoc</t>
         </is>
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>Iset_ptoc1</t>
+          <t>Iset_ptoc1_lvttoc</t>
         </is>
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>Icoarse_ptoc1</t>
+          <t>Icoarse_ptoc1_lvttoc</t>
         </is>
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>T1_ptoc2</t>
+          <t>T1_ptoc2_lvttoc</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>Iset_ptoc2</t>
+          <t>Iset_ptoc2_lvttoc</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>Icoarse_ptoc2</t>
+          <t>Icoarse_ptoc2_lvttoc</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
-          <t>T1_ptoc3</t>
+          <t>T1_ptoc3_lvttoc</t>
         </is>
       </c>
       <c r="H1" s="1" t="inlineStr">
         <is>
-          <t>Iset_ptoc3</t>
+          <t>Iset_ptoc3_lvttoc</t>
         </is>
       </c>
       <c r="I1" s="1" t="inlineStr">
         <is>
-          <t>Icoarse_ptoc3</t>
+          <t>Icoarse_ptoc3_lvttoc</t>
         </is>
       </c>
       <c r="J1" s="1" t="inlineStr">
         <is>
-          <t>Uop_ptuv1</t>
+          <t>Uop_ptuv1_lvttoc</t>
         </is>
       </c>
       <c r="K1" s="1" t="inlineStr">
         <is>
-          <t>U2op_ptuv1</t>
+          <t>U2op_ptuv1_lvttoc</t>
         </is>
       </c>
       <c r="L1" s="1" t="inlineStr">
         <is>
-          <t>Uop_ptuv2</t>
+          <t>Uop_ptuv2_lvttoc</t>
         </is>
       </c>
       <c r="M1" s="1" t="inlineStr">
         <is>
-          <t>U2op_ptuv2</t>
+          <t>U2op_ptuv2_lvttoc</t>
         </is>
       </c>
       <c r="N1" s="1" t="inlineStr">
         <is>
-          <t>Imax_phar1</t>
+          <t>Imax_phar1_lvttoc</t>
         </is>
       </c>
       <c r="O1" s="1" t="inlineStr">
         <is>
-          <t>Ratio_phar1</t>
+          <t>Ratio_phar1_lvttoc</t>
         </is>
       </c>
       <c r="P1" s="1" t="inlineStr">
@@ -1879,322 +1852,322 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>vvod_lvrbvtr1</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>oper_vyvod_lvrbvtr1</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>u_lin_pusk_lvrbvtr1</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>u2_pusk_lvrbvtr1</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>pusk_lvrbvtr1</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>neispr_zn_lvrbvtr1</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>vvod_lvrbvtr2</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>oper_vyvod_lvrbvtr2</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>u_lin_pusk_lvrbvtr2</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>u2_pusk_lvrbvtr2</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>pusk_lvrbvtr2</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M2" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
+          <t>neispr_zn_lvrbvtr2</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>vvod_ptoc1_lvttoc</t>
         </is>
       </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O2" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
+          <t>oper_vyvod_ptoc1_lvttoc</t>
+        </is>
+      </c>
+      <c r="O2" t="inlineStr">
+        <is>
+          <t>mtzA_pusk_ptoc1_lvttoc</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>mtzB_pusk_ptoc1_lvttoc</t>
         </is>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="R2" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="S2" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="T2" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="U2" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
+          <t>mtzC_pusk_ptoc1_lvttoc</t>
+        </is>
+      </c>
+      <c r="R2" t="inlineStr">
+        <is>
+          <t>gen_pusk_ptoc_lvttoc</t>
+        </is>
+      </c>
+      <c r="S2" t="inlineStr">
+        <is>
+          <t>mtz_srabsign_ptoc1_lvttoc</t>
+        </is>
+      </c>
+      <c r="T2" t="inlineStr">
+        <is>
+          <t>mtz_srab_ptoc1_lvttoc</t>
+        </is>
+      </c>
+      <c r="U2" t="inlineStr">
+        <is>
+          <t>io_A_ptoc1_lvttoc</t>
         </is>
       </c>
       <c r="V2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>io_B_ptoc1_lvttoc</t>
         </is>
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>io_C_ptoc1_lvttoc</t>
         </is>
       </c>
       <c r="X2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>vvod_ptoc2_lvttoc</t>
         </is>
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>oper_vyvod_ptoc2_lvttoc</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>mtzA_pusk_ptoc2_lvttoc</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>mtzB_pusk_ptoc2_lvttoc</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>mtzC_pusk_ptoc2_lvttoc</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>gen_pusk_ptoc2_lvttoc</t>
         </is>
       </c>
       <c r="AD2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>mtz_srabsign_ptoc2_lvttoc</t>
         </is>
       </c>
       <c r="AE2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>mtz_srab_ptoc2_lvttoc</t>
         </is>
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>io_A_ptoc2_lvttoc</t>
         </is>
       </c>
       <c r="AG2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>io_B_ptoc2_lvttoc</t>
         </is>
       </c>
       <c r="AH2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>io_C_ptoc2_lvttoc</t>
         </is>
       </c>
       <c r="AI2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>vvod_ptoc3_lvttoc</t>
         </is>
       </c>
       <c r="AJ2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>oper_vyvod_ptoc3_lvttoc</t>
         </is>
       </c>
       <c r="AK2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>mtzA_pusk_ptoc3_lvttoc</t>
         </is>
       </c>
       <c r="AL2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>mtzB_pusk_ptoc3_lvttoc</t>
         </is>
       </c>
       <c r="AM2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>mtzC_pusk_ptoc3_lvttoc</t>
         </is>
       </c>
       <c r="AN2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>gen_pusk_ptoc3_lvttoc</t>
         </is>
       </c>
       <c r="AO2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>mtz_srabsign_ptoc3_lvttoc</t>
         </is>
       </c>
       <c r="AP2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>mtz_srab_ptoc3_lvttoc</t>
         </is>
       </c>
       <c r="AQ2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>io_A_ptoc3_lvttoc</t>
         </is>
       </c>
       <c r="AR2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>io_B_ptoc3_lvttoc</t>
         </is>
       </c>
       <c r="AS2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>io_C_ptoc3_lvttoc</t>
         </is>
       </c>
       <c r="AT2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>kpon_pusk_ptuv1_lvttoc</t>
         </is>
       </c>
       <c r="AU2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>kpon_pusk_ptuv2_lvttoc</t>
         </is>
       </c>
       <c r="AV2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>ia_start_out_phar1_lvttoc</t>
         </is>
       </c>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>ib_start_out_phar1_lvttoc</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>ic_start_out_phar1_lvttoc</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>start_phar1_lvttoc</t>
         </is>
       </c>
       <c r="AZ2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="BA2" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
+          <t>blok_rblc1_lvttoc</t>
+        </is>
+      </c>
+      <c r="BA2" t="inlineStr">
+        <is>
+          <t>mtz_pusk_lvttoc</t>
         </is>
       </c>
       <c r="BB2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>vvod_ptrc1</t>
         </is>
       </c>
       <c r="BC2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="BD2" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
+          <t>oper_vyvod_ptrc1</t>
+        </is>
+      </c>
+      <c r="BD2" t="inlineStr">
+        <is>
+          <t>pusk_ptrc1</t>
         </is>
       </c>
       <c r="BE2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>srab_ptrc1</t>
         </is>
       </c>
       <c r="BF2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>vvod_rblc1</t>
         </is>
       </c>
       <c r="BG2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>oper_vyvod_rblc1</t>
         </is>
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>zapret_rblc1</t>
         </is>
       </c>
       <c r="BI2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>vvod_rbre1</t>
         </is>
       </c>
       <c r="BJ2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>oper_vyvod_rbre1</t>
         </is>
       </c>
       <c r="BK2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="BL2" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
+          <t>zapret_rbre1</t>
+        </is>
+      </c>
+      <c r="BL2" t="inlineStr">
+        <is>
+          <t>pusk_lvalv</t>
         </is>
       </c>
     </row>

--- a/Функция_Режим.xlsx
+++ b/Функция_Режим.xlsx
@@ -992,16 +992,16 @@
         <v>0</v>
       </c>
       <c r="C2" s="2" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="D2" s="2" t="n">
-        <v>0.1</v>
+        <v>0.05</v>
       </c>
       <c r="E2" s="2" t="n">
         <v>0.5</v>
       </c>
       <c r="F2" s="2" t="n">
-        <v>0.1</v>
+        <v>0.02</v>
       </c>
       <c r="G2" t="n">
         <v>0</v>
@@ -1052,13 +1052,13 @@
         <v>10.5</v>
       </c>
       <c r="W2" s="2" t="n">
-        <v>1000</v>
+        <v>750</v>
       </c>
       <c r="X2" s="2" t="n">
-        <v>5000</v>
+        <v>3000</v>
       </c>
       <c r="Y2" s="2" t="n">
-        <v>5000</v>
+        <v>3000</v>
       </c>
       <c r="Z2" s="2" t="n">
         <v>1</v>
@@ -1070,7 +1070,7 @@
         <v>1</v>
       </c>
       <c r="AC2" s="2" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="AD2" s="2" t="n">
         <v>5</v>
@@ -1392,38 +1392,38 @@
       <c r="N2" t="n">
         <v>0</v>
       </c>
-      <c r="O2" t="n">
-        <v>0</v>
+      <c r="O2" s="2" t="n">
+        <v>1.1</v>
       </c>
       <c r="P2" t="n">
         <v>0</v>
       </c>
       <c r="Q2" s="2" t="n">
-        <v>0.165</v>
+        <v>1.1</v>
       </c>
       <c r="R2" s="2" t="n">
         <v>240</v>
       </c>
       <c r="S2" s="2" t="n">
-        <v>0.165</v>
+        <v>1.1</v>
       </c>
       <c r="T2" s="2" t="n">
         <v>120</v>
       </c>
       <c r="U2" s="2" t="n">
-        <v>0.275</v>
+        <v>0.46</v>
       </c>
       <c r="V2" t="n">
         <v>0</v>
       </c>
       <c r="W2" s="2" t="n">
-        <v>0.275</v>
+        <v>0.46</v>
       </c>
       <c r="X2" s="2" t="n">
         <v>240</v>
       </c>
       <c r="Y2" s="2" t="n">
-        <v>0.275</v>
+        <v>0.46</v>
       </c>
       <c r="Z2" s="2" t="n">
         <v>120</v>
@@ -1431,8 +1431,8 @@
       <c r="AA2" t="n">
         <v>0</v>
       </c>
-      <c r="AB2" s="2" t="n">
-        <v>0.165</v>
+      <c r="AB2" t="n">
+        <v>0</v>
       </c>
       <c r="AC2" t="n">
         <v>0</v>
@@ -1960,412 +1960,412 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>vvod_rctr1_ctr</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>oper_vyvod_rctr1_ctr</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>pusk_obryv_rctr1_ctr</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>srab_obryv_rctr1_ctr</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>pusk_assym_rctr1_ctr</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>srab_assym_rctr1_ctr</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>vvod_rctr2_ctr</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>oper_vyvod_rctr2_ctr</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>pusk_obryv_rctr2_ctr</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>srab_obryv_rctr2_ctr</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>pusk_assym_rctr2_ctr</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>srab_assym_rctr2_ctr</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>vvod_rctr3_ctr</t>
         </is>
       </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>oper_vyvod_rctr3_ctr</t>
         </is>
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>pusk_obryv_rctr3_ctr</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>srab_obryv_rctr3_ctr</t>
         </is>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>pusk_assym_rctr3_ctr</t>
         </is>
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>srab_assym_rctr3_ctr</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>srab_ctr</t>
         </is>
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>vvod_pdif2_tdif</t>
         </is>
       </c>
       <c r="U2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>oper_vyvod_pdif2_tdif</t>
         </is>
       </c>
       <c r="V2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>pusk_A_pdif2_tdif</t>
         </is>
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>srab_A_pdif2_tdif</t>
         </is>
       </c>
       <c r="X2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>srabsign_A_pdif2_tdif</t>
         </is>
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>io_A_pdif2_tdif</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>pusk_B_pdif2_tdif</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>srab_B_pdif2_tdif</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>srabsign_B_pdif2_tdif</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>io_B_pdif2_tdif</t>
         </is>
       </c>
       <c r="AD2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>pusk_C_pdif2_tdif</t>
         </is>
       </c>
       <c r="AE2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>srab_C_pdif2_tdif</t>
         </is>
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>srabsign_C_pdif2_tdif</t>
         </is>
       </c>
       <c r="AG2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>io_C_pdif2_tdif</t>
         </is>
       </c>
       <c r="AH2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>pusk_pdif2_tdif</t>
         </is>
       </c>
       <c r="AI2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>srabsign_pdif2_tdif</t>
         </is>
       </c>
       <c r="AJ2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AK2" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
+          <t>srab_pdif2_tdif</t>
+        </is>
+      </c>
+      <c r="AK2" t="inlineStr">
+        <is>
+          <t>vvod_pdif1_tdif</t>
         </is>
       </c>
       <c r="AL2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AM2" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AN2" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AO2" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AP2" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
+          <t>oper_vyvod_pdif1_tdif</t>
+        </is>
+      </c>
+      <c r="AM2" t="inlineStr">
+        <is>
+          <t>pusk_A_pdif1_tdif</t>
+        </is>
+      </c>
+      <c r="AN2" t="inlineStr">
+        <is>
+          <t>srab_A_pdif1_tdif</t>
+        </is>
+      </c>
+      <c r="AO2" t="inlineStr">
+        <is>
+          <t>srabsign_A_pdif1_tdif</t>
+        </is>
+      </c>
+      <c r="AP2" t="inlineStr">
+        <is>
+          <t>io_A_pdif1_tdif</t>
         </is>
       </c>
       <c r="AQ2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>pusk_B_pdif1_tdif</t>
         </is>
       </c>
       <c r="AR2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>srab_B_pdif1_tdif</t>
         </is>
       </c>
       <c r="AS2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>srabsign_B_pdif1_tdif</t>
         </is>
       </c>
       <c r="AT2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>io_B_pdif1_tdif</t>
         </is>
       </c>
       <c r="AU2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>pusk_C_pdif1_tdif</t>
         </is>
       </c>
       <c r="AV2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>srab_C_pdif1_tdif</t>
         </is>
       </c>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>srabsign_C_pdif1_tdif</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AY2" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AZ2" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="BA2" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
+          <t>io_C_pdif1_tdif</t>
+        </is>
+      </c>
+      <c r="AY2" t="inlineStr">
+        <is>
+          <t>pusk_pdif1_tdif</t>
+        </is>
+      </c>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>srabsign_pdif1_tdif</t>
+        </is>
+      </c>
+      <c r="BA2" t="inlineStr">
+        <is>
+          <t>srab_pdif1_tdif</t>
         </is>
       </c>
       <c r="BB2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="BC2" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
+          <t>pusk_A_hf2phar1_tdif</t>
+        </is>
+      </c>
+      <c r="BC2" t="inlineStr">
+        <is>
+          <t>pusk_B_hf2phar1_tdif</t>
         </is>
       </c>
       <c r="BD2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="BE2" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
+          <t>pusk_C_hf2phar1_tdif</t>
+        </is>
+      </c>
+      <c r="BE2" t="inlineStr">
+        <is>
+          <t>pusk_hf2phar1_tdif</t>
         </is>
       </c>
       <c r="BF2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>pusk_A_hf5phar1_tdif</t>
         </is>
       </c>
       <c r="BG2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>pusk_B_hf5phar1_tdif</t>
         </is>
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>pusk_C_hf5phar1_tdif</t>
         </is>
       </c>
       <c r="BI2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>pusk_hf5phar1_tdif</t>
         </is>
       </c>
       <c r="BJ2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>vvod_rctr1_tdif</t>
         </is>
       </c>
       <c r="BK2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>oper_vyvod_rctr1_tdif</t>
         </is>
       </c>
       <c r="BL2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>srab_A_rctr1_tdif</t>
         </is>
       </c>
       <c r="BM2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>srab_B_rctr1_tdif</t>
         </is>
       </c>
       <c r="BN2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>srab_C_rctr1_tdif</t>
         </is>
       </c>
       <c r="BO2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>srab_rctr1_tdif</t>
         </is>
       </c>
       <c r="BP2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="BQ2" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
+          <t>neispr_rctr1_tdif</t>
+        </is>
+      </c>
+      <c r="BQ2" t="inlineStr">
+        <is>
+          <t>vvod_ptrc1_tprmofflvlgc</t>
         </is>
       </c>
       <c r="BR2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="BS2" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="BT2" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="BU2" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
+          <t>oper_vyvod_ptrc1_tprmofflvlgc</t>
+        </is>
+      </c>
+      <c r="BS2" t="inlineStr">
+        <is>
+          <t>pusk_ptrc1_tprmofflvlgc</t>
+        </is>
+      </c>
+      <c r="BT2" t="inlineStr">
+        <is>
+          <t>srab_ptrc1_tprmofflvlgc</t>
+        </is>
+      </c>
+      <c r="BU2" t="inlineStr">
+        <is>
+          <t>vvod_rbre1_tprmofflvlgc</t>
         </is>
       </c>
       <c r="BV2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="BW2" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="BX2" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="BY2" s="2" t="inlineStr">
-        <is>
-          <t>1.0</t>
-        </is>
-      </c>
-      <c r="BZ2" s="2" t="inlineStr">
-        <is>
-          <t>0.5</t>
+          <t>oper_vyvod_rbre1_tprmofflvlgc</t>
+        </is>
+      </c>
+      <c r="BW2" t="inlineStr">
+        <is>
+          <t>zapret_rbre1_tprmofflvlgc</t>
+        </is>
+      </c>
+      <c r="BX2" t="inlineStr">
+        <is>
+          <t>pusk_lvalh</t>
+        </is>
+      </c>
+      <c r="BY2" t="inlineStr">
+        <is>
+          <t>diffA</t>
+        </is>
+      </c>
+      <c r="BZ2" t="inlineStr">
+        <is>
+          <t>restA</t>
         </is>
       </c>
       <c r="CA2" t="inlineStr">
         <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="CB2" s="2" t="inlineStr">
-        <is>
-          <t>1.0</t>
+          <t>diffB</t>
+        </is>
+      </c>
+      <c r="CB2" t="inlineStr">
+        <is>
+          <t>restB</t>
         </is>
       </c>
       <c r="CC2" t="inlineStr">
         <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="CD2" s="2" t="inlineStr">
-        <is>
-          <t>1.0</t>
+          <t>diffC</t>
+        </is>
+      </c>
+      <c r="CD2" t="inlineStr">
+        <is>
+          <t>restC</t>
         </is>
       </c>
     </row>

--- a/Функция_Режим.xlsx
+++ b/Функция_Режим.xlsx
@@ -435,7 +435,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AJ2"/>
+  <dimension ref="A1:BX2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -474,187 +474,427 @@
     <col width="20" customWidth="1" min="34" max="34"/>
     <col width="20" customWidth="1" min="35" max="35"/>
     <col width="20" customWidth="1" min="36" max="36"/>
+    <col width="20" customWidth="1" min="37" max="37"/>
+    <col width="20" customWidth="1" min="38" max="38"/>
+    <col width="20" customWidth="1" min="39" max="39"/>
+    <col width="20" customWidth="1" min="40" max="40"/>
+    <col width="20" customWidth="1" min="41" max="41"/>
+    <col width="20" customWidth="1" min="42" max="42"/>
+    <col width="20" customWidth="1" min="43" max="43"/>
+    <col width="20" customWidth="1" min="44" max="44"/>
+    <col width="20" customWidth="1" min="45" max="45"/>
+    <col width="20" customWidth="1" min="46" max="46"/>
+    <col width="20" customWidth="1" min="47" max="47"/>
+    <col width="20" customWidth="1" min="48" max="48"/>
+    <col width="20" customWidth="1" min="49" max="49"/>
+    <col width="20" customWidth="1" min="50" max="50"/>
+    <col width="20" customWidth="1" min="51" max="51"/>
+    <col width="20" customWidth="1" min="52" max="52"/>
+    <col width="20" customWidth="1" min="53" max="53"/>
+    <col width="20" customWidth="1" min="54" max="54"/>
+    <col width="20" customWidth="1" min="55" max="55"/>
+    <col width="20" customWidth="1" min="56" max="56"/>
+    <col width="20" customWidth="1" min="57" max="57"/>
+    <col width="20" customWidth="1" min="58" max="58"/>
+    <col width="20" customWidth="1" min="59" max="59"/>
+    <col width="20" customWidth="1" min="60" max="60"/>
+    <col width="20" customWidth="1" min="61" max="61"/>
+    <col width="20" customWidth="1" min="62" max="62"/>
+    <col width="20" customWidth="1" min="63" max="63"/>
+    <col width="20" customWidth="1" min="64" max="64"/>
+    <col width="20" customWidth="1" min="65" max="65"/>
+    <col width="20" customWidth="1" min="66" max="66"/>
+    <col width="20" customWidth="1" min="67" max="67"/>
+    <col width="20" customWidth="1" min="68" max="68"/>
+    <col width="20" customWidth="1" min="69" max="69"/>
+    <col width="20" customWidth="1" min="70" max="70"/>
+    <col width="20" customWidth="1" min="71" max="71"/>
+    <col width="20" customWidth="1" min="72" max="72"/>
+    <col width="20" customWidth="1" min="73" max="73"/>
+    <col width="20" customWidth="1" min="74" max="74"/>
+    <col width="20" customWidth="1" min="75" max="75"/>
+    <col width="20" customWidth="1" min="76" max="76"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
+          <t>SGF1_lvttoc</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>SGF1_ptoc1_lvttoc</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>SGF2_ptoc1_lvttoc</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>SGF3_ptoc1_lvttoc</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>SGF4_ptoc1_lvttoc</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>SGF5_ptoc1_lvttoc</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>SGF6_ptoc1_lvttoc</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>SGF1_ptoc2_lvttoc</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>SGF2_ptoc2_lvttoc</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>SGF3_ptoc2_lvttoc</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>SGF4_ptoc2_lvttoc</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>SGF5_ptoc2_lvttoc</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>SGF6_ptoc2_lvttoc</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>SGF1_ptoc3_lvttoc</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>SGF2_ptoc3_lvttoc</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>SGF3_ptoc3_lvttoc</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
+        <is>
+          <t>SGF4_ptoc3_lvttoc</t>
+        </is>
+      </c>
+      <c r="R1" s="1" t="inlineStr">
+        <is>
+          <t>SGF5_ptoc3_lvttoc</t>
+        </is>
+      </c>
+      <c r="S1" s="1" t="inlineStr">
+        <is>
+          <t>SGF6_ptoc3_lvttoc</t>
+        </is>
+      </c>
+      <c r="T1" s="1" t="inlineStr">
+        <is>
+          <t>SGF1_ptuv1_lvttoc</t>
+        </is>
+      </c>
+      <c r="U1" s="1" t="inlineStr">
+        <is>
+          <t>SGF1_phar1_lvttoc</t>
+        </is>
+      </c>
+      <c r="V1" s="1" t="inlineStr">
+        <is>
+          <t>SGF1_rblc1_lvttoc</t>
+        </is>
+      </c>
+      <c r="W1" s="1" t="inlineStr">
+        <is>
+          <t>SGF1_ptoc1_lvtoc</t>
+        </is>
+      </c>
+      <c r="X1" s="1" t="inlineStr">
+        <is>
+          <t>SGF2_ptoc1_lvtoc</t>
+        </is>
+      </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
           <t>SGF1_rcbf1_lvcbsup</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="Z1" s="1" t="inlineStr">
         <is>
           <t>SGF2_rcbf1_lvcbsup</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="AA1" s="1" t="inlineStr">
         <is>
           <t>SGF3_rcbf1_lvcbsup</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="AB1" s="1" t="inlineStr">
         <is>
           <t>SGF4_rcbf1_lvcbsup</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="AC1" s="1" t="inlineStr">
         <is>
           <t>SGF5_rcbf1_lvcbsup</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="AD1" s="1" t="inlineStr">
         <is>
           <t>SGF6_rcbf1_lvcbsup</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="AE1" s="1" t="inlineStr">
         <is>
           <t>SGF7_rcbf1_lvcbsup</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="AF1" s="1" t="inlineStr">
         <is>
           <t>SGF8_rcbf1_lvcbsup</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
-        <is>
-          <t>SGF1_swctrl</t>
-        </is>
-      </c>
-      <c r="J1" s="1" t="inlineStr">
-        <is>
-          <t>SGF1_cbcswi1_swctrl</t>
-        </is>
-      </c>
-      <c r="K1" s="1" t="inlineStr">
-        <is>
-          <t>SGF2_cbcswi1_swctrl</t>
-        </is>
-      </c>
-      <c r="L1" s="1" t="inlineStr">
-        <is>
-          <t>SGF1_cbcswi1_hvbctrl</t>
-        </is>
-      </c>
-      <c r="M1" s="1" t="inlineStr">
-        <is>
-          <t>SGF1_tsd</t>
-        </is>
-      </c>
-      <c r="N1" s="1" t="inlineStr">
-        <is>
-          <t>SGF1_xcbr1_tsd</t>
-        </is>
-      </c>
-      <c r="O1" s="1" t="inlineStr">
-        <is>
-          <t>SGF2_xcbr1_tsd</t>
-        </is>
-      </c>
-      <c r="P1" s="1" t="inlineStr">
-        <is>
-          <t>SGF3_xcbr1_tsd</t>
-        </is>
-      </c>
-      <c r="Q1" s="1" t="inlineStr">
-        <is>
-          <t>SGF4_xcbr1_tsd</t>
-        </is>
-      </c>
-      <c r="R1" s="1" t="inlineStr">
-        <is>
-          <t>SGF5_xcbr1_tsd</t>
-        </is>
-      </c>
-      <c r="S1" s="1" t="inlineStr">
-        <is>
-          <t>SGF6_xcbr1_tsd</t>
-        </is>
-      </c>
-      <c r="T1" s="1" t="inlineStr">
+      <c r="AG1" s="1" t="inlineStr">
         <is>
           <t>SGF1_genrbrf1_tpbrf</t>
         </is>
       </c>
-      <c r="U1" s="1" t="inlineStr">
+      <c r="AH1" s="1" t="inlineStr">
         <is>
           <t>SGF2_genrbrf1_tpbrf</t>
         </is>
       </c>
-      <c r="V1" s="1" t="inlineStr">
+      <c r="AI1" s="1" t="inlineStr">
         <is>
           <t>SGF3_genrbrf1_tpbrf</t>
         </is>
       </c>
-      <c r="W1" s="1" t="inlineStr">
+      <c r="AJ1" s="1" t="inlineStr">
         <is>
           <t>SGF4_genrbrf1_tpbrf</t>
         </is>
       </c>
-      <c r="X1" s="1" t="inlineStr">
+      <c r="AK1" s="1" t="inlineStr">
         <is>
           <t>SGF5_genrbrf1_tpbrf</t>
         </is>
       </c>
-      <c r="Y1" s="1" t="inlineStr">
+      <c r="AL1" s="1" t="inlineStr">
         <is>
           <t>SGF6_genrbrf1_tpbrf</t>
         </is>
       </c>
-      <c r="Z1" s="1" t="inlineStr">
+      <c r="AM1" s="1" t="inlineStr">
+        <is>
+          <t>SGF1_ptrc1_tofflvlgc</t>
+        </is>
+      </c>
+      <c r="AN1" s="1" t="inlineStr">
+        <is>
+          <t>SGF1_rbre1_tofflvlgc</t>
+        </is>
+      </c>
+      <c r="AO1" s="1" t="inlineStr">
+        <is>
+          <t>SGF2_rbre1_tofflvlgc</t>
+        </is>
+      </c>
+      <c r="AP1" s="1" t="inlineStr">
+        <is>
+          <t>SGF3_rbre1_tofflvlgc</t>
+        </is>
+      </c>
+      <c r="AQ1" s="1" t="inlineStr">
+        <is>
+          <t>SGF1_lvcbrblc1_tofflvlgc</t>
+        </is>
+      </c>
+      <c r="AR1" s="1" t="inlineStr">
+        <is>
+          <t>SGF2_lvcbrblc1_tofflvlgc</t>
+        </is>
+      </c>
+      <c r="AS1" s="1" t="inlineStr">
+        <is>
+          <t>SGF3_lvcbrblc1_tofflvlgc</t>
+        </is>
+      </c>
+      <c r="AT1" s="1" t="inlineStr">
         <is>
           <t>SGF1_hvcbptrc1_hvtcboff</t>
         </is>
       </c>
-      <c r="AA1" s="1" t="inlineStr">
+      <c r="AU1" s="1" t="inlineStr">
+        <is>
+          <t>SGF1_lvcbptrc1_lvtcboff</t>
+        </is>
+      </c>
+      <c r="AV1" s="1" t="inlineStr">
+        <is>
+          <t>SGF1_lvcbrecrbre1_lvtcboff</t>
+        </is>
+      </c>
+      <c r="AW1" s="1" t="inlineStr">
+        <is>
+          <t>SGF1_lvbtsrblc1_lvtcboff</t>
+        </is>
+      </c>
+      <c r="AX1" s="1" t="inlineStr">
+        <is>
+          <t>SGF1_tsa</t>
+        </is>
+      </c>
+      <c r="AY1" s="1" t="inlineStr">
+        <is>
+          <t>SGF2_tsa</t>
+        </is>
+      </c>
+      <c r="AZ1" s="1" t="inlineStr">
+        <is>
+          <t>SGF3_tsa</t>
+        </is>
+      </c>
+      <c r="BA1" s="1" t="inlineStr">
+        <is>
+          <t>SGF4_tsa</t>
+        </is>
+      </c>
+      <c r="BB1" s="1" t="inlineStr">
+        <is>
+          <t>SGF5_tsa</t>
+        </is>
+      </c>
+      <c r="BC1" s="1" t="inlineStr">
+        <is>
+          <t>SGF6_tsa</t>
+        </is>
+      </c>
+      <c r="BD1" s="1" t="inlineStr">
+        <is>
+          <t>SGF7_tsa</t>
+        </is>
+      </c>
+      <c r="BE1" s="1" t="inlineStr">
+        <is>
+          <t>SGF8_tsa</t>
+        </is>
+      </c>
+      <c r="BF1" s="1" t="inlineStr">
+        <is>
+          <t>SGF9_tsa</t>
+        </is>
+      </c>
+      <c r="BG1" s="1" t="inlineStr">
+        <is>
+          <t>SGF10_tsa</t>
+        </is>
+      </c>
+      <c r="BH1" s="1" t="inlineStr">
+        <is>
+          <t>SGF11_tsa</t>
+        </is>
+      </c>
+      <c r="BI1" s="1" t="inlineStr">
+        <is>
+          <t>SGF12_tsa</t>
+        </is>
+      </c>
+      <c r="BJ1" s="1" t="inlineStr">
+        <is>
+          <t>SGF13_tsa</t>
+        </is>
+      </c>
+      <c r="BK1" s="1" t="inlineStr">
         <is>
           <t>SGF1_lvalh</t>
         </is>
       </c>
-      <c r="AB1" s="1" t="inlineStr">
+      <c r="BL1" s="1" t="inlineStr">
         <is>
           <t>SGF2_lvalh</t>
         </is>
       </c>
-      <c r="AC1" s="1" t="inlineStr">
+      <c r="BM1" s="1" t="inlineStr">
         <is>
           <t>SGF3_lvalh</t>
         </is>
       </c>
-      <c r="AD1" s="1" t="inlineStr">
+      <c r="BN1" s="1" t="inlineStr">
         <is>
           <t>SGF4_lvalh</t>
         </is>
       </c>
-      <c r="AE1" s="1" t="inlineStr">
+      <c r="BO1" s="1" t="inlineStr">
         <is>
           <t>SGF5_lvalh</t>
         </is>
       </c>
-      <c r="AF1" s="1" t="inlineStr">
+      <c r="BP1" s="1" t="inlineStr">
         <is>
           <t>SGF6_lvalh</t>
         </is>
       </c>
-      <c r="AG1" s="1" t="inlineStr">
+      <c r="BQ1" s="1" t="inlineStr">
         <is>
           <t>SGF7_lvalh</t>
         </is>
       </c>
-      <c r="AH1" s="1" t="inlineStr">
+      <c r="BR1" s="1" t="inlineStr">
         <is>
           <t>SGF8_lvalh</t>
         </is>
       </c>
-      <c r="AI1" s="1" t="inlineStr">
+      <c r="BS1" s="1" t="inlineStr">
         <is>
           <t>SGF9_lvalh</t>
         </is>
       </c>
-      <c r="AJ1" s="1" t="inlineStr">
+      <c r="BT1" s="1" t="inlineStr">
         <is>
           <t>SGF10_lvalh</t>
+        </is>
+      </c>
+      <c r="BU1" s="1" t="inlineStr">
+        <is>
+          <t>SGF11_lvalh</t>
+        </is>
+      </c>
+      <c r="BV1" s="1" t="inlineStr">
+        <is>
+          <t>SGF12_lvalh</t>
+        </is>
+      </c>
+      <c r="BW1" s="1" t="inlineStr">
+        <is>
+          <t>SGF13_lvalh</t>
+        </is>
+      </c>
+      <c r="BX1" s="1" t="inlineStr">
+        <is>
+          <t>SGF14_lvalh</t>
         </is>
       </c>
     </row>
@@ -749,14 +989,14 @@
       <c r="AD2" t="n">
         <v>0</v>
       </c>
-      <c r="AE2" s="2" t="n">
-        <v>1</v>
+      <c r="AE2" t="n">
+        <v>0</v>
       </c>
       <c r="AF2" t="n">
         <v>0</v>
       </c>
-      <c r="AG2" s="2" t="n">
-        <v>1</v>
+      <c r="AG2" t="n">
+        <v>0</v>
       </c>
       <c r="AH2" t="n">
         <v>0</v>
@@ -764,8 +1004,128 @@
       <c r="AI2" t="n">
         <v>0</v>
       </c>
-      <c r="AJ2" s="2" t="n">
-        <v>1</v>
+      <c r="AJ2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ2" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA2" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB2" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC2" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD2" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE2" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF2" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG2" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH2" t="n">
+        <v>0</v>
+      </c>
+      <c r="BI2" t="n">
+        <v>0</v>
+      </c>
+      <c r="BJ2" t="n">
+        <v>0</v>
+      </c>
+      <c r="BK2" t="n">
+        <v>0</v>
+      </c>
+      <c r="BL2" t="n">
+        <v>0</v>
+      </c>
+      <c r="BM2" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="BN2" t="n">
+        <v>0</v>
+      </c>
+      <c r="BO2" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="BP2" t="n">
+        <v>0</v>
+      </c>
+      <c r="BQ2" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="BR2" t="n">
+        <v>0</v>
+      </c>
+      <c r="BS2" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="BT2" t="n">
+        <v>0</v>
+      </c>
+      <c r="BU2" t="n">
+        <v>0</v>
+      </c>
+      <c r="BV2" t="n">
+        <v>0</v>
+      </c>
+      <c r="BW2" t="n">
+        <v>0</v>
+      </c>
+      <c r="BX2" t="n">
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -779,7 +1139,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O2"/>
+  <dimension ref="A1:V2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -797,82 +1157,124 @@
     <col width="20" customWidth="1" min="13" max="13"/>
     <col width="20" customWidth="1" min="14" max="14"/>
     <col width="20" customWidth="1" min="15" max="15"/>
+    <col width="20" customWidth="1" min="16" max="16"/>
+    <col width="20" customWidth="1" min="17" max="17"/>
+    <col width="20" customWidth="1" min="18" max="18"/>
+    <col width="20" customWidth="1" min="19" max="19"/>
+    <col width="20" customWidth="1" min="20" max="20"/>
+    <col width="20" customWidth="1" min="21" max="21"/>
+    <col width="20" customWidth="1" min="22" max="22"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
+          <t>T1_ptoc1_lvttoc</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Iset_ptoc1_lvttoc</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Icoarse_ptoc1_lvttoc</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>T1_ptoc2_lvttoc</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>Iset_ptoc2_lvttoc</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>Icoarse_ptoc2_lvttoc</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>T1_ptoc3_lvttoc</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>Iset_ptoc3_lvttoc</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>Icoarse_ptoc3_lvttoc</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>Uop_ptuv1_lvttoc</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>U2op_ptuv1_lvttoc</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>Imax_phar1_lvttoc</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>Ratio_phar1_lvttoc</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>T1_ptoc1_lvtoc</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>Iset_ptoc1_lvtoc</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
           <t>T1_rcbf1_lvcbsup</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="Q1" s="1" t="inlineStr">
         <is>
           <t>T2_rcbf1_lvcbsup</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="R1" s="1" t="inlineStr">
         <is>
           <t>T3_rcbf1_lvcbsup</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>T1_cbcswi1_swctrl</t>
-        </is>
-      </c>
-      <c r="E1" s="1" t="inlineStr">
-        <is>
-          <t>T2_cbcswi1_swctrl</t>
-        </is>
-      </c>
-      <c r="F1" s="1" t="inlineStr">
-        <is>
-          <t>T3_cbcswi1_swctrl</t>
-        </is>
-      </c>
-      <c r="G1" s="1" t="inlineStr">
-        <is>
-          <t>T4_cbcswi1_swctrl</t>
-        </is>
-      </c>
-      <c r="H1" s="1" t="inlineStr">
-        <is>
-          <t>T1_cbcswi1_hvbctrl</t>
-        </is>
-      </c>
-      <c r="I1" s="1" t="inlineStr">
-        <is>
-          <t>T1_xcbr1_tsd</t>
-        </is>
-      </c>
-      <c r="J1" s="1" t="inlineStr">
-        <is>
-          <t>T2_xcbr1_tsd</t>
-        </is>
-      </c>
-      <c r="K1" s="1" t="inlineStr">
-        <is>
-          <t>T3_xcbr1_tsd</t>
-        </is>
-      </c>
-      <c r="L1" s="1" t="inlineStr">
-        <is>
-          <t>T4_xcbr1_tsd</t>
-        </is>
-      </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="S1" s="1" t="inlineStr">
         <is>
           <t>T1_genrbrf1_tpbrf</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="T1" s="1" t="inlineStr">
         <is>
           <t>Iset_genrbrf1_tpbrf</t>
         </is>
       </c>
-      <c r="O1" s="1" t="inlineStr">
+      <c r="U1" s="1" t="inlineStr">
         <is>
           <t>T1_hvcbptrc1_hvtcboff</t>
+        </is>
+      </c>
+      <c r="V1" s="1" t="inlineStr">
+        <is>
+          <t>T1_lvcbptrc1_lvtcboff</t>
         </is>
       </c>
     </row>
@@ -914,12 +1316,33 @@
         <v>1</v>
       </c>
       <c r="M2" s="2" t="n">
-        <v>1</v>
+        <v>40</v>
       </c>
       <c r="N2" s="2" t="n">
-        <v>0.2</v>
+        <v>1</v>
       </c>
       <c r="O2" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="P2" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q2" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="R2" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="S2" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="T2" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="U2" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="V2" s="2" t="n">
         <v>1</v>
       </c>
     </row>
@@ -987,197 +1410,197 @@
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
+          <t>OV_lvttoc</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>OV_ptoc1_lvtoc</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>OV_tofflvlg</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>OVlo_tofflvlg</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>OVzapv_tofflvlg</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>OVzavr_tofflvlg</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>OV_hvcbptrc1_hvtcboff</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>vnesh_otkl_zdz</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>vnesh_otkl_urov</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>OV_lvtcboff</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>OV_lvcbptrc1_lvtcboff</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>OV_lvcbrecrbre1_lvtcboff</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>OV_lvbtsrblc1_lvtcboff</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
           <t>OV_rcbf1_lvcbsup</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>ot_emo1emv</t>
-        </is>
-      </c>
-      <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>ot_emo2</t>
-        </is>
-      </c>
-      <c r="E1" s="1" t="inlineStr">
-        <is>
-          <t>avar_isol_V</t>
-        </is>
-      </c>
-      <c r="F1" s="1" t="inlineStr">
-        <is>
-          <t>niz_isol_V</t>
-        </is>
-      </c>
-      <c r="G1" s="1" t="inlineStr">
-        <is>
-          <t>pruzh_ne_zaved</t>
-        </is>
-      </c>
-      <c r="H1" s="1" t="inlineStr">
-        <is>
-          <t>Sbros</t>
-        </is>
-      </c>
-      <c r="I1" s="1" t="inlineStr">
-        <is>
-          <t>otkl_ot_knopk</t>
-        </is>
-      </c>
-      <c r="J1" s="1" t="inlineStr">
-        <is>
-          <t>oper_otkl_V</t>
-        </is>
-      </c>
-      <c r="K1" s="1" t="inlineStr">
-        <is>
-          <t>KRV_resurs_V</t>
-        </is>
-      </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="P1" s="1" t="inlineStr">
         <is>
           <t>vnesh_blok_upr_V</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
-        <is>
-          <t>kontr_emv</t>
-        </is>
-      </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="Q1" s="1" t="inlineStr">
+        <is>
+          <t>OV_rbrf1_tpbrf</t>
+        </is>
+      </c>
+      <c r="R1" s="1" t="inlineStr">
+        <is>
+          <t>pusk_urov_vnesh</t>
+        </is>
+      </c>
+      <c r="S1" s="1" t="inlineStr">
         <is>
           <t>kontr_emo1</t>
         </is>
       </c>
-      <c r="O1" s="1" t="inlineStr">
+      <c r="T1" s="1" t="inlineStr">
         <is>
           <t>kontr_emo2</t>
         </is>
       </c>
-      <c r="P1" s="1" t="inlineStr">
-        <is>
-          <t>rabota_emv</t>
-        </is>
-      </c>
-      <c r="Q1" s="1" t="inlineStr">
-        <is>
-          <t>rabota_emo1</t>
-        </is>
-      </c>
-      <c r="R1" s="1" t="inlineStr">
-        <is>
-          <t>rabota_emo2</t>
-        </is>
-      </c>
-      <c r="S1" s="1" t="inlineStr">
-        <is>
-          <t>OV_swctrl</t>
-        </is>
-      </c>
-      <c r="T1" s="1" t="inlineStr">
-        <is>
-          <t>otkl_v_ot_pu</t>
-        </is>
-      </c>
       <c r="U1" s="1" t="inlineStr">
         <is>
-          <t>otkl_v_ichm</t>
+          <t>Polozh_SA1</t>
         </is>
       </c>
       <c r="V1" s="1" t="inlineStr">
         <is>
-          <t>mestnoe</t>
+          <t>Polozh_SA2</t>
         </is>
       </c>
       <c r="W1" s="1" t="inlineStr">
         <is>
-          <t>otkl_v_ot_tu</t>
+          <t>Polozh_SA3</t>
         </is>
       </c>
       <c r="X1" s="1" t="inlineStr">
         <is>
-          <t>otkl_v_asu</t>
+          <t>Polozh_SA4</t>
         </is>
       </c>
       <c r="Y1" s="1" t="inlineStr">
         <is>
-          <t>kluch_md_priv</t>
+          <t>Polozh_SA5</t>
         </is>
       </c>
       <c r="Z1" s="1" t="inlineStr">
         <is>
-          <t>vkl_v_ot_pu</t>
+          <t>Polozh_SG1</t>
         </is>
       </c>
       <c r="AA1" s="1" t="inlineStr">
         <is>
-          <t>vkl_v_ichm</t>
+          <t>Polozh_SG2</t>
         </is>
       </c>
       <c r="AB1" s="1" t="inlineStr">
         <is>
-          <t>distanz</t>
+          <t>ot_gz</t>
         </is>
       </c>
       <c r="AC1" s="1" t="inlineStr">
         <is>
-          <t>vkl_v_ot_tu</t>
+          <t>ot_tz</t>
         </is>
       </c>
       <c r="AD1" s="1" t="inlineStr">
         <is>
-          <t>vkl_v_asu</t>
+          <t>ot_v</t>
         </is>
       </c>
       <c r="AE1" s="1" t="inlineStr">
         <is>
-          <t>v_otkl_bk</t>
+          <t>ot_zdz_nn</t>
         </is>
       </c>
       <c r="AF1" s="1" t="inlineStr">
         <is>
-          <t>v_vkl_bk</t>
+          <t>ot_urov_nn</t>
         </is>
       </c>
       <c r="AG1" s="1" t="inlineStr">
         <is>
-          <t>OV_cbcswi1_hvbctrl</t>
+          <t>ot_ieu_tn</t>
         </is>
       </c>
       <c r="AH1" s="1" t="inlineStr">
         <is>
-          <t>oper_vkl_v</t>
+          <t>vnesh_sign1</t>
         </is>
       </c>
       <c r="AI1" s="1" t="inlineStr">
         <is>
-          <t>OV_tsd</t>
+          <t>vnesh_sign2</t>
         </is>
       </c>
       <c r="AJ1" s="1" t="inlineStr">
         <is>
-          <t>pusk_urov_vnesh</t>
+          <t>vnesh_sign3</t>
         </is>
       </c>
       <c r="AK1" s="1" t="inlineStr">
         <is>
-          <t>vnesh_otkl_zdz1</t>
+          <t>vnesh_sign4</t>
         </is>
       </c>
       <c r="AL1" s="1" t="inlineStr">
         <is>
-          <t>vnesh_otkl_urov1</t>
+          <t>IA</t>
         </is>
       </c>
       <c r="AM1" s="1" t="inlineStr">
         <is>
-          <t>vnesh_otkl_zdz2</t>
+          <t>IB</t>
         </is>
       </c>
       <c r="AN1" s="1" t="inlineStr">
         <is>
-          <t>vnesh_otkl_urov2</t>
+          <t>IC</t>
         </is>
       </c>
     </row>
@@ -1314,7 +1737,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AO2"/>
+  <dimension ref="A1:BD2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -1358,192 +1781,207 @@
     <col width="20" customWidth="1" min="39" max="39"/>
     <col width="20" customWidth="1" min="40" max="40"/>
     <col width="20" customWidth="1" min="41" max="41"/>
+    <col width="20" customWidth="1" min="42" max="42"/>
+    <col width="20" customWidth="1" min="43" max="43"/>
+    <col width="20" customWidth="1" min="44" max="44"/>
+    <col width="20" customWidth="1" min="45" max="45"/>
+    <col width="20" customWidth="1" min="46" max="46"/>
+    <col width="20" customWidth="1" min="47" max="47"/>
+    <col width="20" customWidth="1" min="48" max="48"/>
+    <col width="20" customWidth="1" min="49" max="49"/>
+    <col width="20" customWidth="1" min="50" max="50"/>
+    <col width="20" customWidth="1" min="51" max="51"/>
+    <col width="20" customWidth="1" min="52" max="52"/>
+    <col width="20" customWidth="1" min="53" max="53"/>
+    <col width="20" customWidth="1" min="54" max="54"/>
+    <col width="20" customWidth="1" min="55" max="55"/>
+    <col width="20" customWidth="1" min="56" max="56"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>vvod_rcbf1_lvcbsup</t>
+          <t>mtz_pusk_lvttoc</t>
         </is>
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>oper_vyvod_rcbf1_lvcbsup</t>
+          <t>mtz_srab_ptoc1_lvttoc</t>
         </is>
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>v_samoproisv_otkl_rcbf1_lvcbsup</t>
+          <t>mtz_srab_ptoc2_lvttoc</t>
         </is>
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>neispr_V_rcbf1_lvcbsup</t>
+          <t>mtz_srab_ptoc3_lvttoc</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>v_avar_otkl_rcbf1_lvcbsup</t>
+          <t>pusk_ptoc1_lvtoc</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>rfk_rcbf1_lvcbsup</t>
+          <t>srab_ptoc1_lvtoc</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
-          <t>blok_vkl_rcbf1_lvcbsup</t>
+          <t>vvod_ptrc1_tofflvlgc</t>
         </is>
       </c>
       <c r="H1" s="1" t="inlineStr">
         <is>
+          <t>oper_vyvod_ptrc1_tofflvlgc</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>pusk_ptrc1_tofflvlgc</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>srab_ptrc1_tofflvlgc</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>vvod_rblc1_tofflvlgc</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>oper_vyvod_rblc1_tofflvlgc</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>zapret_rblc1_tofflvlgc</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>vvod_rbre1_tofflvlgc</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>oper_vyvod_rbre1_tofflvlgc</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>zapret_rbre1_tofflvlgc</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
+        <is>
+          <t>vvod_hvcbptrc1_hvtcboff</t>
+        </is>
+      </c>
+      <c r="R1" s="1" t="inlineStr">
+        <is>
+          <t>oper_vyvod_hvcbptrc1_hvtcboff</t>
+        </is>
+      </c>
+      <c r="S1" s="1" t="inlineStr">
+        <is>
+          <t>otkl_hvcbptrc1_hvtcboff</t>
+        </is>
+      </c>
+      <c r="T1" s="1" t="inlineStr">
+        <is>
+          <t>otkl_avar_hvcbptrc1_hvtcboff</t>
+        </is>
+      </c>
+      <c r="U1" s="1" t="inlineStr">
+        <is>
+          <t>vvod_lvcbptrc1_lvtcboff</t>
+        </is>
+      </c>
+      <c r="V1" s="1" t="inlineStr">
+        <is>
+          <t>oper_vyvod_lvcbptrc1_lvtcboff</t>
+        </is>
+      </c>
+      <c r="W1" s="1" t="inlineStr">
+        <is>
+          <t>otkl_lvcbptrc1_lvtcboff</t>
+        </is>
+      </c>
+      <c r="X1" s="1" t="inlineStr">
+        <is>
+          <t>otkl_avar_lvcbptrc1_lvtcboff</t>
+        </is>
+      </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>vvod_lvcbrecrbre1_lvtcboff</t>
+        </is>
+      </c>
+      <c r="Z1" s="1" t="inlineStr">
+        <is>
+          <t>oper_vyvod_lvcbrecrbre1_lvtcboff</t>
+        </is>
+      </c>
+      <c r="AA1" s="1" t="inlineStr">
+        <is>
+          <t>zapret_lvcbrecrbre1_lvtcboff</t>
+        </is>
+      </c>
+      <c r="AB1" s="1" t="inlineStr">
+        <is>
+          <t>vvod_lvbtsrblc1_lvtcboff</t>
+        </is>
+      </c>
+      <c r="AC1" s="1" t="inlineStr">
+        <is>
+          <t>oper_vyvod_lvbtsrblc1_lvtcboff</t>
+        </is>
+      </c>
+      <c r="AD1" s="1" t="inlineStr">
+        <is>
+          <t>zapret_lvbtsrblc1_lvtcboff</t>
+        </is>
+      </c>
+      <c r="AE1" s="1" t="inlineStr">
+        <is>
           <t>blok_otkl_rcbf1_lvcbsup</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
-        <is>
-          <t>neisp_emu_rcbf1_lvcbsup</t>
-        </is>
-      </c>
-      <c r="J1" s="1" t="inlineStr">
-        <is>
-          <t>zashita_emv_rcbf1_lvcbsup</t>
-        </is>
-      </c>
-      <c r="K1" s="1" t="inlineStr">
-        <is>
-          <t>zashita_emo1_rcbf1_lvcbsup</t>
-        </is>
-      </c>
-      <c r="L1" s="1" t="inlineStr">
-        <is>
-          <t>zashita_emo2_rcbf1_lvcbsup</t>
-        </is>
-      </c>
-      <c r="M1" s="1" t="inlineStr">
-        <is>
-          <t>vvod_swctrl</t>
-        </is>
-      </c>
-      <c r="N1" s="1" t="inlineStr">
-        <is>
-          <t>oper_vyvod_swctrl</t>
-        </is>
-      </c>
-      <c r="O1" s="1" t="inlineStr">
-        <is>
-          <t>vvod_cbcswi1_swctrl</t>
-        </is>
-      </c>
-      <c r="P1" s="1" t="inlineStr">
-        <is>
-          <t>uv_otkluchit_cbcswi1_swctrl</t>
-        </is>
-      </c>
-      <c r="Q1" s="1" t="inlineStr">
-        <is>
-          <t>uv_idet_per_cbcswi1_swctrl</t>
-        </is>
-      </c>
-      <c r="R1" s="1" t="inlineStr">
-        <is>
-          <t>uv_prev_vrem_per_cbcswi1_swctrl</t>
-        </is>
-      </c>
-      <c r="S1" s="1" t="inlineStr">
-        <is>
-          <t>uv_vkluchit_cbcswi1_swctrl</t>
-        </is>
-      </c>
-      <c r="T1" s="1" t="inlineStr">
-        <is>
-          <t>uv_ne_opredeleno_cbcswi1_swctrl</t>
-        </is>
-      </c>
-      <c r="U1" s="1" t="inlineStr">
-        <is>
-          <t>uv_otklucheno_cbcswi1_swctrl</t>
-        </is>
-      </c>
-      <c r="V1" s="1" t="inlineStr">
-        <is>
-          <t>uv_vklucheno_cbcswi1_swctrl</t>
-        </is>
-      </c>
-      <c r="W1" s="1" t="inlineStr">
-        <is>
-          <t>uv_neispr_neopred_cbcswi1_swctrl</t>
-        </is>
-      </c>
-      <c r="X1" s="1" t="inlineStr">
-        <is>
-          <t>vvod_cbcswi1_hvbctrl</t>
-        </is>
-      </c>
-      <c r="Y1" s="1" t="inlineStr">
-        <is>
-          <t>oper_vyvod_cbcswi1_hvbctrl</t>
-        </is>
-      </c>
-      <c r="Z1" s="1" t="inlineStr">
-        <is>
-          <t>uv_vkl_cbcswi1_hvbctrl</t>
-        </is>
-      </c>
-      <c r="AA1" s="1" t="inlineStr">
-        <is>
-          <t>vvod_tsd</t>
-        </is>
-      </c>
-      <c r="AB1" s="1" t="inlineStr">
-        <is>
-          <t>oper_vyvod_tsd</t>
-        </is>
-      </c>
-      <c r="AC1" s="1" t="inlineStr">
-        <is>
-          <t>vvod_xcbr1_tsd</t>
-        </is>
-      </c>
-      <c r="AD1" s="1" t="inlineStr">
-        <is>
-          <t>v_prom_pol_xcbr1_tsd</t>
-        </is>
-      </c>
-      <c r="AE1" s="1" t="inlineStr">
-        <is>
-          <t>v_otkluchen_xcbr1_tsd</t>
-        </is>
-      </c>
       <c r="AF1" s="1" t="inlineStr">
         <is>
-          <t>v_vkluchen_xcbr1_tsd</t>
+          <t>vvod_rbrf1_tpbrf</t>
         </is>
       </c>
       <c r="AG1" s="1" t="inlineStr">
         <is>
-          <t>v_neisp_pol_xcbr1_tsd</t>
+          <t>oper_vyvod_rbrf1_tpbrf</t>
         </is>
       </c>
       <c r="AH1" s="1" t="inlineStr">
         <is>
-          <t>v_otkluchit_rele_xcbr1_tsd</t>
+          <t>uskorenie_rbrf1_tpbrf</t>
         </is>
       </c>
       <c r="AI1" s="1" t="inlineStr">
         <is>
-          <t>v_vkluchit_rele_xcbr1_tsd</t>
+          <t>srab_rbrf1_tpbrf</t>
         </is>
       </c>
       <c r="AJ1" s="1" t="inlineStr">
         <is>
-          <t>ss_prev_vrem_per_ka</t>
+          <t>pusk_rbrf1_tpbrf</t>
         </is>
       </c>
       <c r="AK1" s="1" t="inlineStr">
         <is>
-          <t>pusk_t_lvalh</t>
+          <t>io_rbrf1_tpbrf</t>
         </is>
       </c>
       <c r="AL1" s="1" t="inlineStr">
@@ -1553,17 +1991,92 @@
       </c>
       <c r="AM1" s="1" t="inlineStr">
         <is>
-          <t>vvod_hvcbptrc1_hvtcboff</t>
+          <t>SS_gz_sign</t>
         </is>
       </c>
       <c r="AN1" s="1" t="inlineStr">
         <is>
-          <t>otkl_hvcbptrc1_hvtcboff</t>
+          <t>SS_gz_zablok</t>
         </is>
       </c>
       <c r="AO1" s="1" t="inlineStr">
         <is>
-          <t>otkl_avar_hvcbptrc1_hvtcboff</t>
+          <t>SS_gz_nizk_isol</t>
+        </is>
+      </c>
+      <c r="AP1" s="1" t="inlineStr">
+        <is>
+          <t>SS_tz_sign</t>
+        </is>
+      </c>
+      <c r="AQ1" s="1" t="inlineStr">
+        <is>
+          <t>SS_tz_nizk_isol</t>
+        </is>
+      </c>
+      <c r="AR1" s="1" t="inlineStr">
+        <is>
+          <t>SS_tz_zablok</t>
+        </is>
+      </c>
+      <c r="AS1" s="1" t="inlineStr">
+        <is>
+          <t>SS_ts_sign</t>
+        </is>
+      </c>
+      <c r="AT1" s="1" t="inlineStr">
+        <is>
+          <t>SS_vnesh_otkl</t>
+        </is>
+      </c>
+      <c r="AU1" s="1" t="inlineStr">
+        <is>
+          <t>SS_vyh_zepi_razobr</t>
+        </is>
+      </c>
+      <c r="AV1" s="1" t="inlineStr">
+        <is>
+          <t>SS_bi_vyved</t>
+        </is>
+      </c>
+      <c r="AW1" s="1" t="inlineStr">
+        <is>
+          <t>SS_ot_sign</t>
+        </is>
+      </c>
+      <c r="AX1" s="1" t="inlineStr">
+        <is>
+          <t>SS_neispr_ot_gz</t>
+        </is>
+      </c>
+      <c r="AY1" s="1" t="inlineStr">
+        <is>
+          <t>SS_neispr_ot_tz</t>
+        </is>
+      </c>
+      <c r="AZ1" s="1" t="inlineStr">
+        <is>
+          <t>SS_neispr_ot_v</t>
+        </is>
+      </c>
+      <c r="BA1" s="1" t="inlineStr">
+        <is>
+          <t>SS_ot_nn_sign</t>
+        </is>
+      </c>
+      <c r="BB1" s="1" t="inlineStr">
+        <is>
+          <t>SS_prev_vrem_per_ka</t>
+        </is>
+      </c>
+      <c r="BC1" s="1" t="inlineStr">
+        <is>
+          <t>SS_obsh_vnesh_sign</t>
+        </is>
+      </c>
+      <c r="BD1" s="1" t="inlineStr">
+        <is>
+          <t>pusk_lvalv</t>
         </is>
       </c>
     </row>
@@ -1769,6 +2282,81 @@
         </is>
       </c>
       <c r="AO2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AP2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AQ2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AR2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AS2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AT2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AU2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AV2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AW2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AX2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AY2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BA2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BB2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BC2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BD2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
